--- a/data/trans_dic/P64D$particular_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,42; 88,78</t>
+          <t>74,19; 88,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,98; 80,66</t>
+          <t>67,92; 80,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,71; 83,83</t>
+          <t>73,77; 84,26</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,19; 84,61</t>
+          <t>71,07; 84,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,61; 79,54</t>
+          <t>66,74; 79,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,53; 81,48</t>
+          <t>71,59; 81,23</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,93; 87,19</t>
+          <t>75,28; 87,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,5; 67,68</t>
+          <t>53,65; 69,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67,39; 77,53</t>
+          <t>66,91; 77,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,27; 77,49</t>
+          <t>58,94; 77,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,28; 70,71</t>
+          <t>17,18; 69,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,67; 70,34</t>
+          <t>31,96; 70,09</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,64; 85,06</t>
+          <t>71,93; 85,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,45; 82,46</t>
+          <t>71,05; 82,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,4; 82,17</t>
+          <t>73,02; 81,92</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,43; 87,0</t>
+          <t>74,43; 87,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,92; 72,56</t>
+          <t>55,72; 72,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,02; 79,33</t>
+          <t>69,61; 79,38</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>76,54; 85,61</t>
+          <t>75,9; 85,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,54; 71,2</t>
+          <t>61,66; 71,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70,34; 77,35</t>
+          <t>70,51; 77,86</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>56,17; 90,3</t>
+          <t>56,79; 91,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,84; 45,35</t>
+          <t>34,6; 44,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,49; 84,27</t>
+          <t>49,32; 82,74</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>74,16; 85,11</t>
+          <t>73,96; 84,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50,57; 64,29</t>
+          <t>50,31; 64,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65,66; 76,61</t>
+          <t>65,89; 75,8</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>143017; 170615</t>
+          <t>142569; 170413</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98121; 116420</t>
+          <t>98036; 116675</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>251391; 282077</t>
+          <t>248246; 283545</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>172362; 207790</t>
+          <t>174523; 208705</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>111986; 131738</t>
+          <t>110549; 131893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>294137; 335066</t>
+          <t>294371; 334009</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111410; 129642</t>
+          <t>111925; 130550</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63453; 81805</t>
+          <t>64846; 83714</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181634; 208977</t>
+          <t>180340; 207541</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>100881; 129704</t>
+          <t>98656; 129264</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49891; 182976</t>
+          <t>44450; 181026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134963; 299756</t>
+          <t>136193; 298725</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81842; 97171</t>
+          <t>82173; 97651</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75465; 88329</t>
+          <t>76111; 88080</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162478; 181881</t>
+          <t>161636; 181333</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100532; 117504</t>
+          <t>100520; 118089</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48316; 62694</t>
+          <t>48141; 62837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>152861; 175696</t>
+          <t>154155; 175802</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>255828; 286169</t>
+          <t>253708; 286617</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>188762; 218373</t>
+          <t>189106; 219429</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>450840; 495797</t>
+          <t>451942; 499062</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>352910; 567357</t>
+          <t>356843; 574362</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>94436; 122933</t>
+          <t>93784; 121831</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>445142; 757907</t>
+          <t>443591; 744134</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1457763; 1673040</t>
+          <t>1453831; 1670403</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>738808; 939288</t>
+          <t>735063; 936876</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2249815; 2625071</t>
+          <t>2257817; 2597394</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$particular_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,19; 88,68</t>
+          <t>74,37; 87,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,92; 80,84</t>
+          <t>68,84; 80,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,77; 84,26</t>
+          <t>74,39; 83,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,07; 84,99</t>
+          <t>71,5; 85,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,74; 79,63</t>
+          <t>65,09; 77,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,59; 81,23</t>
+          <t>71,14; 80,14</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,28; 87,8</t>
+          <t>75,36; 87,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,65; 69,26</t>
+          <t>51,84; 66,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,91; 77,0</t>
+          <t>66,22; 75,94</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>63,57%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,94; 77,23</t>
+          <t>56,41; 74,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 69,95</t>
+          <t>51,66; 67,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,96; 70,09</t>
+          <t>57,8; 69,31</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,93; 85,48</t>
+          <t>69,46; 82,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>71,05; 82,23</t>
+          <t>69,9; 81,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,02; 81,92</t>
+          <t>72,05; 80,34</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,43; 87,43</t>
+          <t>73,54; 86,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,72; 72,73</t>
+          <t>55,4; 72,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,61; 79,38</t>
+          <t>69,41; 79,26</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,9; 85,75</t>
+          <t>74,38; 83,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>61,66; 71,54</t>
+          <t>59,2; 68,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70,51; 77,86</t>
+          <t>68,35; 75,19</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>56,79; 91,41</t>
+          <t>52,13; 61,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,6; 44,94</t>
+          <t>33,54; 44,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49,32; 82,74</t>
+          <t>45,78; 53,18</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>73,96; 84,98</t>
+          <t>70,66; 75,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50,31; 64,13</t>
+          <t>58,52; 63,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65,89; 75,8</t>
+          <t>66,02; 69,3</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>160319</t>
+          <t>163754</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>108581</t>
+          <t>115000</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268901</t>
+          <t>278753</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142569; 170413</t>
+          <t>149113; 175044</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98036; 116675</t>
+          <t>105155; 123031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>248246; 283545</t>
+          <t>262801; 293860</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>193389</t>
+          <t>200656</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>122419</t>
+          <t>124587</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315809</t>
+          <t>325243</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>174523; 208705</t>
+          <t>182011; 216408</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>110549; 131893</t>
+          <t>112974; 134405</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>294371; 334009</t>
+          <t>304566; 343085</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>121852</t>
+          <t>122556</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73214</t>
+          <t>73302</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195065</t>
+          <t>195857</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111925; 130550</t>
+          <t>112742; 130365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64846; 83714</t>
+          <t>63782; 81714</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180340; 207541</t>
+          <t>180549; 207038</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>140391</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>125096</t>
+          <t>108150</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241125</t>
+          <t>248542</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>98656; 129264</t>
+          <t>118373; 156810</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44450; 181026</t>
+          <t>93584; 121447</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136193; 298725</t>
+          <t>225995; 271014</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>104329</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82351</t>
+          <t>91038</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>172571</t>
+          <t>195368</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82173; 97651</t>
+          <t>94572; 112618</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76111; 88080</t>
+          <t>83485; 97462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161636; 181333</t>
+          <t>184154; 205353</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>109659</t>
+          <t>109830</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>55839</t>
+          <t>55956</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165498</t>
+          <t>165786</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100520; 118089</t>
+          <t>100072; 118046</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>48141; 62837</t>
+          <t>48395; 63046</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>154155; 175802</t>
+          <t>155087; 177105</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>271557</t>
+          <t>306744</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>204686</t>
+          <t>232525</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>476243</t>
+          <t>539269</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>253708; 286617</t>
+          <t>288202; 323939</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>189106; 219429</t>
+          <t>214216; 248768</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>451942; 499062</t>
+          <t>512179; 563383</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>468300</t>
+          <t>259746</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>107623</t>
+          <t>119891</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>575923</t>
+          <t>379637</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>356843; 574362</t>
+          <t>237176; 280958</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>93784; 121831</t>
+          <t>104691; 137438</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>443591; 744134</t>
+          <t>351182; 407914</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1531325</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>879809</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2411135</t>
+          <t>2328455</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1453831; 1670403</t>
+          <t>1363077; 1449760</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>735063; 936876</t>
+          <t>884410; 953875</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2257817; 2597394</t>
+          <t>2271399; 2384275</t>
         </is>
       </c>
     </row>
